--- a/docs/procurement_study/bed-TRELLIS-cloud.xlsx
+++ b/docs/procurement_study/bed-TRELLIS-cloud.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>query "bett metall schwarz" · 2026-07-15 22:24 UTC · destination Bildungscampus, 74076 Heilbronn (DE)</t>
+          <t>query "bett antik metall schwarz" · 2026-07-15 23:16 UTC · destination Bildungscampus, 74076 Heilbronn (DE)</t>
         </is>
       </c>
     </row>
@@ -536,11 +536,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yaheetech bettgestell metallbett einzelbettgestell doppelbettgestell in 4 groessen verfueg</t>
+          <t>moebel akut metallbett verena metallbett gestell schwarz 140x200 cm massive qualitaet S0JC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5762</v>
+        <v>0.6634</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>49.99</v>
+        <v>199</v>
       </c>
       <c r="H5" t="n">
         <v>29.95</v>
@@ -562,14 +562,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>79.94</v>
+        <v>228.95</v>
       </c>
       <c r="K5" t="n">
-        <v>79.94</v>
+        <v>228.95</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-bettgestell-metallbett-einzelbettgestell-doppelbettgestell-in-4-groessen-verfuegbar-S0Z4Q0U8/</t>
+          <t>https://www.otto.de/p/moebel-akut-metallbett-verena-metallbett-gestell-schwarz-140x200-cm-massive-qualitaet-S0JCY05Z/</t>
         </is>
       </c>
     </row>
@@ -586,11 +586,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yaheetech bettgestell metallbett einzelbettgestell doppelbettgestell in 4 groessen verfueg</t>
+          <t>moebel akut metallbett verena metallbett gestell schwarz 140x200 cm massive qualitaet S0JC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5762</v>
+        <v>0.6634</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>49.99</v>
+        <v>199</v>
       </c>
       <c r="H6" t="n">
         <v>29.95</v>
@@ -612,14 +612,14 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>529.85</v>
+        <v>2019.95</v>
       </c>
       <c r="K6" t="n">
-        <v>52.98</v>
+        <v>202</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-bettgestell-metallbett-einzelbettgestell-doppelbettgestell-in-4-groessen-verfuegbar-S0Z4Q0U8/</t>
+          <t>https://www.otto.de/p/moebel-akut-metallbett-verena-metallbett-gestell-schwarz-140x200-cm-massive-qualitaet-S0JCY05Z/</t>
         </is>
       </c>
     </row>
@@ -636,11 +636,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>yaheetech metallbett bettgestell 90x190 90x200 140x200cm minimalistischer bettrahmen mit k</t>
+          <t>home affaire metallbett ottos choice mit aufwendiger verzierung romantischer stil 50930946</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6446</v>
+        <v>0.6712</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>54.99</v>
+        <v>299.99</v>
       </c>
       <c r="H7" t="n">
         <v>29.95</v>
@@ -662,14 +662,14 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>84.94</v>
+        <v>329.94</v>
       </c>
       <c r="K7" t="n">
-        <v>84.94</v>
+        <v>329.94</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-metallbett-bettgestell-90x190-90x200-140x200cm-minimalistischer-bettrahmen-mit-kopfteil-gaestebett-mit-lattenrost-S0B8M0UK/</t>
+          <t>https://www.otto.de/p/home-affaire-metallbett-ottos-choice-mit-aufwendiger-verzierung-romantischer-stil-509309467/</t>
         </is>
       </c>
     </row>
@@ -686,11 +686,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yaheetech metallbett bettgestell 90x190 90x200 140x200cm minimalistischer bettrahmen mit k</t>
+          <t>home affaire metallbett ottos choice mit aufwendiger verzierung romantischer stil 50930946</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6446</v>
+        <v>0.6712</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>54.99</v>
+        <v>299.99</v>
       </c>
       <c r="H8" t="n">
         <v>29.95</v>
@@ -712,14 +712,14 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>579.85</v>
+        <v>3029.85</v>
       </c>
       <c r="K8" t="n">
-        <v>57.98</v>
+        <v>302.99</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-metallbett-bettgestell-90x190-90x200-140x200cm-minimalistischer-bettrahmen-mit-kopfteil-gaestebett-mit-lattenrost-S0B8M0UK/</t>
+          <t>https://www.otto.de/p/home-affaire-metallbett-ottos-choice-mit-aufwendiger-verzierung-romantischer-stil-509309467/</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>189.97</v>
+        <v>199.99</v>
       </c>
       <c r="H9" t="n">
         <v>29.95</v>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>219.92</v>
+        <v>229.94</v>
       </c>
       <c r="K9" t="n">
-        <v>219.92</v>
+        <v>229.94</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>189.97</v>
+        <v>199.99</v>
       </c>
       <c r="H10" t="n">
         <v>29.95</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1929.65</v>
+        <v>2029.85</v>
       </c>
       <c r="K10" t="n">
-        <v>192.97</v>
+        <v>202.98</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>0.7711</v>
       </c>
       <c r="D2" t="n">
-        <v>189.97</v>
+        <v>199.99</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -913,14 +913,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>moebel akut metallbett verena metallbett gestell schwarz 140x200 cm massive qualitaet S0JC</t>
+          <t>loft24 metallbett tanja bettgestell aus metall bett doppelbett S002P047</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6634</v>
+        <v>0.7679</v>
       </c>
       <c r="D3" t="n">
-        <v>199</v>
+        <v>419.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -929,26 +929,26 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/moebel-akut-metallbett-verena-metallbett-gestell-schwarz-140x200-cm-massive-qualitaet-S0JCY05Z/</t>
+          <t>https://www.otto.de/p/loft24-metallbett-tanja-bettgestell-aus-metall-bett-doppelbett-S002P047/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STJÄRNÖ Bettgestell</t>
+          <t>home affaire metallbett ottos choice mit aufwendiger verzierung romantischer stil 50930946</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6479</v>
+        <v>0.6712</v>
       </c>
       <c r="D4" t="n">
-        <v>229</v>
+        <v>299.99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -957,54 +957,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/stjaernoe-bettgestell-anthrazit-90570190/</t>
+          <t>https://www.otto.de/p/home-affaire-metallbett-ottos-choice-mit-aufwendiger-verzierung-romantischer-stil-509309467/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POCO Einrichtungsmärkte</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>progarden tisch trio weiss polypropylen h l ca 72x216 cm 601720600</t>
+          <t>moebel akut metallbett verena metallbett gestell schwarz 140x200 cm massive qualitaet S0JC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6634</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>clip-zero-shot</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.poco.de/p/progarden-tisch-trio-weiss-polypropylen-h-l-ca-72x216-cm-601720600</t>
+          <t>https://www.otto.de/p/moebel-akut-metallbett-verena-metallbett-gestell-schwarz-140x200-cm-massive-qualitaet-S0JCY05Z/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yaheetech metallbett bettgestell 90x190 90x200 140x200cm minimalistischer bettrahmen mit k</t>
+          <t>MALM Bettgestell hoch</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6446</v>
+        <v>0.648</v>
       </c>
       <c r="D6" t="n">
-        <v>54.99</v>
+        <v>179</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-metallbett-bettgestell-90x190-90x200-140x200cm-minimalistischer-bettrahmen-mit-kopfteil-gaestebett-mit-lattenrost-S0B8M0UK/</t>
+          <t>https://www.ikea.com/de/de/p/malm-bettgestell-hoch-weiss-luroey-s69002431/</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TUFJORD Bettgestell, gepolstert</t>
+          <t>STJÄRNÖ Bettgestell</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6372</v>
+        <v>0.6479</v>
       </c>
       <c r="D7" t="n">
-        <v>499</v>
+        <v>229</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1041,26 +1041,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/tufjord-bettgestell-gepolstert-tallmyra-weiss-schwarz-60573251/</t>
+          <t>https://www.ikea.com/de/de/p/stjaernoe-bettgestell-anthrazit-90570190/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RÅDMANSÖ Bettgestell</t>
+          <t>en casa metallbett villach bettgestell 140x200 cm stahlrahmen schwarz walnuss optik S0O0B0</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6342</v>
+        <v>0.6475</v>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>142.99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1069,26 +1069,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/radmansoe-bettgestell-braun-nussbaumnachbildung-60599166/</t>
+          <t>https://www.otto.de/p/en-casa-metallbett-villach-bettgestell-140x200-cm-stahlrahmen-schwarz-walnuss-optik-S0O0B0L5/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RAMNEFJÄLL Bettgestell, gepolstert</t>
+          <t>jvmoebel holzbett landhaus metallbett aus holz in schwarz fuer elegantes schlafzimmer 1 tl</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.629</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>199</v>
+        <v>3359</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/ramnefjaell-bettgestell-gepolstert-kilanda-dunkelblau-luroey-s89607482/</t>
+          <t>https://www.otto.de/p/jvmoebel-holzbett-landhaus-metallbett-aus-holz-in-schwarz-fuer-elegantes-schlafzimmer-1-tlg-bett-made-in-europa-S0RFF0L4/</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1109,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NORRUDDEN Gästebett</t>
+          <t>RÅDMANSÖ Bettgestell</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6278</v>
+        <v>0.6342</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/norrudden-gaestebett-schwarz-90531354/</t>
+          <t>https://www.ikea.com/de/de/p/radmansoe-bettgestell-braun-nussbaumnachbildung-60599166/</t>
         </is>
       </c>
     </row>
@@ -1137,14 +1137,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TÄRNKULLEN Bettgestell, gepolstert</t>
+          <t>VITARNA Himmelbettgestell</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6259</v>
+        <v>0.634</v>
       </c>
       <c r="D11" t="n">
-        <v>319</v>
+        <v>179</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/taernkullen-bettgestell-gepolstert-kelinge-beige-luroey-s09608131/</t>
+          <t>https://www.ikea.com/de/de/p/vitarna-himmelbettgestell-weiss-60573680/</t>
         </is>
       </c>
     </row>
@@ -1165,14 +1165,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VITARNA Himmelbettgestell</t>
+          <t>NORRUDDEN Gästebett</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6243</v>
+        <v>0.6278</v>
       </c>
       <c r="D12" t="n">
-        <v>251.1</v>
+        <v>129</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/vitarna-himmelbettgestell-weiss-luroey-skadis-holz-s59556337/</t>
+          <t>https://www.ikea.com/de/de/p/norrudden-gaestebett-schwarz-90531354/</t>
         </is>
       </c>
     </row>
@@ -1193,14 +1193,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VEVELSTAD Bettgestell</t>
+          <t>IDANÄS Bettgestell</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6196</v>
+        <v>0.6269</v>
       </c>
       <c r="D13" t="n">
-        <v>149</v>
+        <v>499</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1209,26 +1209,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/vevelstad-bettgestell-weiss-00505528/</t>
+          <t>https://www.ikea.com/de/de/p/idanaes-bettgestell-weiss-00458904/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>POCO Einrichtungsmärkte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VEVELSTAD Bettgestell mit 2 Kopfteilen</t>
+          <t>boxbett dunkelgrau liegeflaeche b l ca 200x180 cm 510970000</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.609</v>
+        <v>0.6258</v>
       </c>
       <c r="D14" t="n">
-        <v>269</v>
+        <v>999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/vevelstad-bettgestell-mit-2-kopfteilen-weiss-tolkning-rattan-s39441738/</t>
+          <t>https://www.poco.de/p/boxbett-dunkelgrau-liegeflaeche-b-l-ca-200x180-cm-510970000</t>
         </is>
       </c>
     </row>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TÄLLÅSEN Bettgestell, gepolstert</t>
+          <t>VITARNA Himmelbettgestell</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6243</v>
       </c>
       <c r="D15" t="n">
-        <v>199</v>
+        <v>251.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1265,26 +1265,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/taellasen-bettgestell-gepolstert-kulsta-hellbeige-50564775/</t>
+          <t>https://www.ikea.com/de/de/p/vitarna-himmelbettgestell-weiss-luroey-skadis-holz-s59556337/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yaheetech metallbett 90 160cm b bettrahmen vintage bettgestell mit kronenfoermigem kopftei</t>
+          <t>SONGESAND Bettgestell</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5918</v>
+        <v>0.6206</v>
       </c>
       <c r="D16" t="n">
-        <v>69.98999999999999</v>
+        <v>249</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1293,26 +1293,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-metallbett-90-160cm-b-bettrahmen-vintage-bettgestell-mit-kronenfoermigem-kopfteil-S0L9Z0HJ/</t>
+          <t>https://www.ikea.com/de/de/p/songesand-bettgestell-weiss-luroey-s19241293/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>zinus bettgestell mateo modernes bett mit lattenrost gaestebett schwarz 1 tlg metallbett s</t>
+          <t>VEVELSTAD Bettgestell</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5861</v>
+        <v>0.6196</v>
       </c>
       <c r="D17" t="n">
-        <v>74.98999999999999</v>
+        <v>149</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1321,26 +1321,26 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/zinus-bettgestell-mateo-modernes-bett-mit-lattenrost-gaestebett-schwarz-1-tlg-metallbett-schwarz-140x200-cm-kinderleichter-aufbau-S0KCA0VB/</t>
+          <t>https://www.ikea.com/de/de/p/vevelstad-bettgestell-weiss-00505528/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yaheetech bettgestell metallbett einzelbettgestell doppelbettgestell in 4 groessen verfueg</t>
+          <t>TÄRNKULLEN Bettgestell, gepolstert</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5762</v>
+        <v>0.615</v>
       </c>
       <c r="D18" t="n">
-        <v>49.99</v>
+        <v>299</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1349,26 +1349,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/yaheetech-bettgestell-metallbett-einzelbettgestell-doppelbettgestell-in-4-groessen-verfuegbar-S0Z4Q0U8/</t>
+          <t>https://www.ikea.com/de/de/p/taernkullen-bettgestell-gepolstert-tibbleby-beige-grau-luroey-s79564336/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>POCO Einrichtungsmärkte</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boxspringbett wien grau liegeflaeche b l ca 180x200 cm 510606200</t>
+          <t>VEVELSTAD Bettgestell mit 2 Kopfteilen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.5739</v>
+        <v>0.609</v>
       </c>
       <c r="D19" t="n">
-        <v>666</v>
+        <v>269</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.poco.de/p/boxspringbett-wien-grau-liegeflaeche-b-l-ca-180x200-cm-510606200</t>
+          <t>https://www.ikea.com/de/de/p/vevelstad-bettgestell-mit-2-kopfteilen-weiss-tolkning-rattan-s39441738/</t>
         </is>
       </c>
     </row>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>skolm bettgestell bragi inkl lattenrost 25 cm hoch metallbett 140x200 cm auch verfuegbar i</t>
+          <t>moebel direkt online metallbett anke fb schwarz 1 tlg in drei breiten S0S040RD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.571</v>
+        <v>0.6014</v>
       </c>
       <c r="D20" t="n">
-        <v>139.99</v>
+        <v>249</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1405,26 +1405,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/skolm-bettgestell-bragi-inkl-lattenrost-25-cm-hoch-metallbett-140x200-cm-auch-verfuegbar-in-180x200-S0EEI0RS/</t>
+          <t>https://www.otto.de/p/moebel-direkt-online-metallbett-anke-fb-schwarz-1-tlg-in-drei-breiten-S0S040RD/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>msmask metallbett bettgestell mit led beleuchtung und steckdose usb anschluesse ohne matra</t>
+          <t>TARVA Bettgestell</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5609</v>
+        <v>0.5992</v>
       </c>
       <c r="D21" t="n">
-        <v>129.99</v>
+        <v>149</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/msmask-metallbett-bettgestell-mit-led-beleuchtung-und-steckdose-usb-anschluesse-ohne-matratze-kinderbett-jugendbett-einzelbett-120-x-200cm-S04ET006/</t>
+          <t>https://www.ikea.com/de/de/p/tarva-bettgestell-kiefer-s89929232/</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Companies scanned: IKEA Deutschland (12 candidates); OTTO (10 candidates); POCO Einrichtungsmärkte (12 candidates); home24 (0 candidates); Möbel Boss (0 candidates); Kaiserkraft (B2B) (0 candidates)</t>
+          <t>Companies scanned: IKEA Deutschland (12 candidates); OTTO (12 candidates); POCO Einrichtungsmärkte (12 candidates); home24 (0 candidates); Möbel Boss (0 candidates); Kaiserkraft (B2B) (0 candidates)</t>
         </is>
       </c>
     </row>
